--- a/diseases/d132/2020-2025.xlsx
+++ b/diseases/d132/2020-2025.xlsx
@@ -45629,9 +45629,6 @@
       <c r="O302" t="n">
         <v>1</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -80231,9 +80228,6 @@
       </c>
       <c r="O532" t="n">
         <v>1</v>
-      </c>
-      <c r="Q532" t="n">
-        <v>0</v>
       </c>
       <c r="R532" t="n">
         <v>0.0002879555610852622</v>
